--- a/5/search/FY2_Missile1_results/best_solution.xlsx
+++ b/5/search/FY2_Missile1_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>297</v>
+        <v>265.5</v>
       </c>
       <c r="B2" t="n">
-        <v>117.6</v>
+        <v>138</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>12427.11426215497</v>
+        <v>11956.69057915823</v>
       </c>
       <c r="F2" t="n">
-        <v>561.7410620435834</v>
+        <v>849.7016317793134</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12694.06067600182</v>
+        <v>11891.72644789557</v>
       </c>
       <c r="I2" t="n">
-        <v>37.82922582082301</v>
+        <v>24.25407944828351</v>
       </c>
       <c r="J2" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
